--- a/ExcelTable/SpinPresentation.xlsx
+++ b/ExcelTable/SpinPresentation.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SpinProfiles" sheetId="1" r:id="Rd52cc93bc9bc45a3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ReelMotionConfig" sheetId="2" r:id="Rf982294f436a4b77"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ReelStrips" sheetId="3" r:id="Rcac76b4898d7446c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SpinProfiles" sheetId="1" r:id="Rea38fd4f54b04516"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ReelMotionConfig" sheetId="2" r:id="R5c820dc50d0d4ce5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ReelStrips" sheetId="3" r:id="Rb5911720578545de"/>
   </x:sheets>
 </x:workbook>
 </file>
